--- a/Sent files/malls_sentiment.xlsx
+++ b/Sent files/malls_sentiment.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P93"/>
+  <dimension ref="A1:Q93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,15 +496,20 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>bert_score</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>bert_pos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>bert_neg</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>bert_label</t>
         </is>
@@ -569,12 +574,15 @@
         </is>
       </c>
       <c r="N2" t="n">
+        <v>0.1993</v>
+      </c>
+      <c r="O2" t="n">
         <v>0.6</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>0.4</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -639,12 +647,15 @@
         </is>
       </c>
       <c r="N3" t="n">
+        <v>-0.1986</v>
+      </c>
+      <c r="O3" t="n">
         <v>0.4</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>0.6</v>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>negative</t>
         </is>
@@ -709,12 +720,15 @@
         </is>
       </c>
       <c r="N4" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="O4" t="n">
         <v>1</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -779,12 +793,15 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>0.5991</v>
+      </c>
+      <c r="O5" t="n">
         <v>0.8</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>0.2</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -849,12 +866,15 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="O6" t="n">
         <v>0.2</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>0.8</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>negative</t>
         </is>
@@ -919,12 +939,15 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -989,12 +1012,15 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>0.5992</v>
+      </c>
+      <c r="O8" t="n">
         <v>0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>0.2</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -1059,12 +1085,15 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="O9" t="n">
         <v>1</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>0</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -1129,12 +1158,15 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>-0.9995000000000001</v>
+      </c>
+      <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>1</v>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>negative</t>
         </is>
@@ -1199,12 +1231,15 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>0.5992</v>
+      </c>
+      <c r="O11" t="n">
         <v>0.8</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>0.2</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -1269,12 +1304,15 @@
         </is>
       </c>
       <c r="N12" t="n">
+        <v>0.9982</v>
+      </c>
+      <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>0</v>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -1339,12 +1377,15 @@
         </is>
       </c>
       <c r="N13" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="O13" t="n">
         <v>1</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>0</v>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -1409,12 +1450,15 @@
         </is>
       </c>
       <c r="N14" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>0</v>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -1479,12 +1523,15 @@
         </is>
       </c>
       <c r="N15" t="n">
+        <v>-0.9991</v>
+      </c>
+      <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>1</v>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>negative</t>
         </is>
@@ -1549,12 +1596,15 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>0.6253</v>
+      </c>
+      <c r="O16" t="n">
         <v>0.8</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>0.2</v>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -1619,12 +1669,15 @@
         </is>
       </c>
       <c r="N17" t="n">
+        <v>0.9808</v>
+      </c>
+      <c r="O17" t="n">
         <v>1</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>0</v>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -1689,12 +1742,15 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>0.2018</v>
+      </c>
+      <c r="O18" t="n">
         <v>0.6</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>0.4</v>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -1759,12 +1815,15 @@
         </is>
       </c>
       <c r="N19" t="n">
+        <v>0.1996</v>
+      </c>
+      <c r="O19" t="n">
         <v>0.6</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>0.4</v>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -1829,12 +1888,15 @@
         </is>
       </c>
       <c r="N20" t="n">
+        <v>0.9987</v>
+      </c>
+      <c r="O20" t="n">
         <v>1</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>0</v>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -1899,12 +1961,15 @@
         </is>
       </c>
       <c r="N21" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="O21" t="n">
         <v>1</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>0</v>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -1969,12 +2034,15 @@
         </is>
       </c>
       <c r="N22" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="O22" t="n">
         <v>1</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>0</v>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -2039,12 +2107,15 @@
         </is>
       </c>
       <c r="N23" t="n">
+        <v>0.9986</v>
+      </c>
+      <c r="O23" t="n">
         <v>1</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>0</v>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -2109,12 +2180,15 @@
         </is>
       </c>
       <c r="N24" t="n">
+        <v>0.1996</v>
+      </c>
+      <c r="O24" t="n">
         <v>0.6</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>0.4</v>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -2179,12 +2253,15 @@
         </is>
       </c>
       <c r="N25" t="n">
+        <v>0.9982</v>
+      </c>
+      <c r="O25" t="n">
         <v>1</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>0</v>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -2249,12 +2326,15 @@
         </is>
       </c>
       <c r="N26" t="n">
+        <v>-0.3335</v>
+      </c>
+      <c r="O26" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>negative</t>
         </is>
@@ -2319,12 +2399,15 @@
         </is>
       </c>
       <c r="N27" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="O27" t="n">
         <v>1</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>0</v>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -2389,12 +2472,15 @@
         </is>
       </c>
       <c r="N28" t="n">
+        <v>0.5992</v>
+      </c>
+      <c r="O28" t="n">
         <v>0.8</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>0.2</v>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -2459,12 +2545,15 @@
         </is>
       </c>
       <c r="N29" t="n">
+        <v>0.1981</v>
+      </c>
+      <c r="O29" t="n">
         <v>0.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>0.4</v>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -2529,12 +2618,15 @@
         </is>
       </c>
       <c r="N30" t="n">
+        <v>0.9987</v>
+      </c>
+      <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>0</v>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -2599,12 +2691,15 @@
         </is>
       </c>
       <c r="N31" t="n">
+        <v>0.9984</v>
+      </c>
+      <c r="O31" t="n">
         <v>1</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>0</v>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -2669,12 +2764,15 @@
         </is>
       </c>
       <c r="N32" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>0</v>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -2739,12 +2837,15 @@
         </is>
       </c>
       <c r="N33" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="O33" t="n">
         <v>1</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>0</v>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -2809,12 +2910,15 @@
         </is>
       </c>
       <c r="N34" t="n">
+        <v>0.9967</v>
+      </c>
+      <c r="O34" t="n">
         <v>1</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>0</v>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -2879,12 +2983,15 @@
         </is>
       </c>
       <c r="N35" t="n">
+        <v>0.5996</v>
+      </c>
+      <c r="O35" t="n">
         <v>0.8</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>0.2</v>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -2949,12 +3056,15 @@
         </is>
       </c>
       <c r="N36" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="O36" t="n">
         <v>1</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>0</v>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -3019,12 +3129,15 @@
         </is>
       </c>
       <c r="N37" t="n">
+        <v>0.5992</v>
+      </c>
+      <c r="O37" t="n">
         <v>0.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>0.2</v>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -3089,12 +3202,15 @@
         </is>
       </c>
       <c r="N38" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="O38" t="n">
         <v>1</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>0</v>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -3159,12 +3275,15 @@
         </is>
       </c>
       <c r="N39" t="n">
+        <v>0.1995</v>
+      </c>
+      <c r="O39" t="n">
         <v>0.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>0.4</v>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -3229,12 +3348,15 @@
         </is>
       </c>
       <c r="N40" t="n">
+        <v>0.9983</v>
+      </c>
+      <c r="O40" t="n">
         <v>1</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>0</v>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -3299,12 +3421,15 @@
         </is>
       </c>
       <c r="N41" t="n">
+        <v>0.1992</v>
+      </c>
+      <c r="O41" t="n">
         <v>0.6</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>0.4</v>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -3369,12 +3494,15 @@
         </is>
       </c>
       <c r="N42" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="O42" t="n">
         <v>1</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>0</v>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -3439,12 +3567,15 @@
         </is>
       </c>
       <c r="N43" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="O43" t="n">
         <v>1</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>0</v>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -3509,12 +3640,15 @@
         </is>
       </c>
       <c r="N44" t="n">
+        <v>0.5988</v>
+      </c>
+      <c r="O44" t="n">
         <v>0.8</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>0.2</v>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -3579,12 +3713,15 @@
         </is>
       </c>
       <c r="N45" t="n">
+        <v>-0.9995000000000001</v>
+      </c>
+      <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>1</v>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>negative</t>
         </is>
@@ -3649,12 +3786,15 @@
         </is>
       </c>
       <c r="N46" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="O46" t="n">
+      <c r="P46" t="n">
         <v>0</v>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -3719,12 +3859,15 @@
         </is>
       </c>
       <c r="N47" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="O47" t="n">
         <v>1</v>
       </c>
-      <c r="O47" t="n">
+      <c r="P47" t="n">
         <v>0</v>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -3789,12 +3932,15 @@
         </is>
       </c>
       <c r="N48" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="O48" t="n">
         <v>1</v>
       </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
         <v>0</v>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -3859,12 +4005,15 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0.5</v>
+        <v>-0.0003</v>
       </c>
       <c r="O49" t="n">
         <v>0.5</v>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="P49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q49" t="inlineStr">
         <is>
           <t>neutral</t>
         </is>
@@ -3929,12 +4078,15 @@
         </is>
       </c>
       <c r="N50" t="n">
+        <v>0.1996</v>
+      </c>
+      <c r="O50" t="n">
         <v>0.6</v>
       </c>
-      <c r="O50" t="n">
+      <c r="P50" t="n">
         <v>0.4</v>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -3999,12 +4151,15 @@
         </is>
       </c>
       <c r="N51" t="n">
+        <v>0.5992</v>
+      </c>
+      <c r="O51" t="n">
         <v>0.8</v>
       </c>
-      <c r="O51" t="n">
+      <c r="P51" t="n">
         <v>0.2</v>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -4069,12 +4224,15 @@
         </is>
       </c>
       <c r="N52" t="n">
+        <v>0.9987</v>
+      </c>
+      <c r="O52" t="n">
         <v>1</v>
       </c>
-      <c r="O52" t="n">
+      <c r="P52" t="n">
         <v>0</v>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -4139,12 +4297,15 @@
         </is>
       </c>
       <c r="N53" t="n">
+        <v>-0.9995000000000001</v>
+      </c>
+      <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="O53" t="n">
+      <c r="P53" t="n">
         <v>1</v>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>negative</t>
         </is>
@@ -4209,12 +4370,15 @@
         </is>
       </c>
       <c r="N54" t="n">
+        <v>-0.1981</v>
+      </c>
+      <c r="O54" t="n">
         <v>0.4</v>
       </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
         <v>0.6</v>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>negative</t>
         </is>
@@ -4279,12 +4443,15 @@
         </is>
       </c>
       <c r="N55" t="n">
+        <v>0.6029</v>
+      </c>
+      <c r="O55" t="n">
         <v>0.8</v>
       </c>
-      <c r="O55" t="n">
+      <c r="P55" t="n">
         <v>0.2</v>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -4349,12 +4516,15 @@
         </is>
       </c>
       <c r="N56" t="n">
+        <v>-0.9971</v>
+      </c>
+      <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="O56" t="n">
+      <c r="P56" t="n">
         <v>1</v>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>negative</t>
         </is>
@@ -4419,12 +4589,15 @@
         </is>
       </c>
       <c r="N57" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="O57" t="n">
         <v>1</v>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
         <v>0</v>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -4489,12 +4662,15 @@
         </is>
       </c>
       <c r="N58" t="n">
+        <v>0.5993000000000001</v>
+      </c>
+      <c r="O58" t="n">
         <v>0.8</v>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
         <v>0.2</v>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -4559,12 +4735,15 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0.5</v>
+        <v>0.001</v>
       </c>
       <c r="O59" t="n">
         <v>0.5</v>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="P59" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q59" t="inlineStr">
         <is>
           <t>neutral</t>
         </is>
@@ -4629,12 +4808,15 @@
         </is>
       </c>
       <c r="N60" t="n">
+        <v>0.5992</v>
+      </c>
+      <c r="O60" t="n">
         <v>0.8</v>
       </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
         <v>0.2</v>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -4699,12 +4881,15 @@
         </is>
       </c>
       <c r="N61" t="n">
+        <v>0.5991</v>
+      </c>
+      <c r="O61" t="n">
         <v>0.8</v>
       </c>
-      <c r="O61" t="n">
+      <c r="P61" t="n">
         <v>0.2</v>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -4769,12 +4954,15 @@
         </is>
       </c>
       <c r="N62" t="n">
+        <v>0.5986</v>
+      </c>
+      <c r="O62" t="n">
         <v>0.8</v>
       </c>
-      <c r="O62" t="n">
+      <c r="P62" t="n">
         <v>0.2</v>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -4839,12 +5027,15 @@
         </is>
       </c>
       <c r="N63" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="O63" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="O63" t="n">
+      <c r="P63" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -4909,12 +5100,15 @@
         </is>
       </c>
       <c r="N64" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="O64" t="n">
         <v>1</v>
       </c>
-      <c r="O64" t="n">
+      <c r="P64" t="n">
         <v>0</v>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -4979,12 +5173,15 @@
         </is>
       </c>
       <c r="N65" t="n">
+        <v>0.5995</v>
+      </c>
+      <c r="O65" t="n">
         <v>0.8</v>
       </c>
-      <c r="O65" t="n">
+      <c r="P65" t="n">
         <v>0.2</v>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -5049,12 +5246,15 @@
         </is>
       </c>
       <c r="N66" t="n">
+        <v>0.6011</v>
+      </c>
+      <c r="O66" t="n">
         <v>0.8</v>
       </c>
-      <c r="O66" t="n">
+      <c r="P66" t="n">
         <v>0.2</v>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -5119,12 +5319,15 @@
         </is>
       </c>
       <c r="N67" t="n">
+        <v>-0.9983</v>
+      </c>
+      <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="O67" t="n">
+      <c r="P67" t="n">
         <v>1</v>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>negative</t>
         </is>
@@ -5189,12 +5392,15 @@
         </is>
       </c>
       <c r="N68" t="n">
+        <v>0.5992</v>
+      </c>
+      <c r="O68" t="n">
         <v>0.8</v>
       </c>
-      <c r="O68" t="n">
+      <c r="P68" t="n">
         <v>0.2</v>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -5259,12 +5465,15 @@
         </is>
       </c>
       <c r="N69" t="n">
+        <v>-0.5998</v>
+      </c>
+      <c r="O69" t="n">
         <v>0.2</v>
       </c>
-      <c r="O69" t="n">
+      <c r="P69" t="n">
         <v>0.8</v>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>negative</t>
         </is>
@@ -5329,12 +5538,15 @@
         </is>
       </c>
       <c r="N70" t="n">
+        <v>0.5992</v>
+      </c>
+      <c r="O70" t="n">
         <v>0.8</v>
       </c>
-      <c r="O70" t="n">
+      <c r="P70" t="n">
         <v>0.2</v>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -5399,12 +5611,15 @@
         </is>
       </c>
       <c r="N71" t="n">
+        <v>0.2011</v>
+      </c>
+      <c r="O71" t="n">
         <v>0.6</v>
       </c>
-      <c r="O71" t="n">
+      <c r="P71" t="n">
         <v>0.4</v>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -5469,12 +5684,15 @@
         </is>
       </c>
       <c r="N72" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="O72" t="n">
         <v>1</v>
       </c>
-      <c r="O72" t="n">
+      <c r="P72" t="n">
         <v>0</v>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -5539,12 +5757,15 @@
         </is>
       </c>
       <c r="N73" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="O73" t="n">
         <v>1</v>
       </c>
-      <c r="O73" t="n">
+      <c r="P73" t="n">
         <v>0</v>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -5609,12 +5830,15 @@
         </is>
       </c>
       <c r="N74" t="n">
+        <v>0.9987</v>
+      </c>
+      <c r="O74" t="n">
         <v>1</v>
       </c>
-      <c r="O74" t="n">
+      <c r="P74" t="n">
         <v>0</v>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -5679,12 +5903,15 @@
         </is>
       </c>
       <c r="N75" t="n">
+        <v>0.9987</v>
+      </c>
+      <c r="O75" t="n">
         <v>1</v>
       </c>
-      <c r="O75" t="n">
+      <c r="P75" t="n">
         <v>0</v>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -5749,12 +5976,15 @@
         </is>
       </c>
       <c r="N76" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="O76" t="n">
         <v>1</v>
       </c>
-      <c r="O76" t="n">
+      <c r="P76" t="n">
         <v>0</v>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -5819,12 +6049,15 @@
         </is>
       </c>
       <c r="N77" t="n">
+        <v>0.5973000000000001</v>
+      </c>
+      <c r="O77" t="n">
         <v>0.8</v>
       </c>
-      <c r="O77" t="n">
+      <c r="P77" t="n">
         <v>0.2</v>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -5889,12 +6122,15 @@
         </is>
       </c>
       <c r="N78" t="n">
+        <v>0.5992</v>
+      </c>
+      <c r="O78" t="n">
         <v>0.8</v>
       </c>
-      <c r="O78" t="n">
+      <c r="P78" t="n">
         <v>0.2</v>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -5959,12 +6195,15 @@
         </is>
       </c>
       <c r="N79" t="n">
+        <v>0.1979</v>
+      </c>
+      <c r="O79" t="n">
         <v>0.6</v>
       </c>
-      <c r="O79" t="n">
+      <c r="P79" t="n">
         <v>0.4</v>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -6029,12 +6268,15 @@
         </is>
       </c>
       <c r="N80" t="n">
+        <v>0.5991</v>
+      </c>
+      <c r="O80" t="n">
         <v>0.8</v>
       </c>
-      <c r="O80" t="n">
+      <c r="P80" t="n">
         <v>0.2</v>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -6099,12 +6341,15 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0.5</v>
+        <v>0.0054</v>
       </c>
       <c r="O81" t="n">
         <v>0.5</v>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="P81" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q81" t="inlineStr">
         <is>
           <t>neutral</t>
         </is>
@@ -6169,12 +6414,15 @@
         </is>
       </c>
       <c r="N82" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="O82" t="n">
         <v>1</v>
       </c>
-      <c r="O82" t="n">
+      <c r="P82" t="n">
         <v>0</v>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -6239,12 +6487,15 @@
         </is>
       </c>
       <c r="N83" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="O83" t="n">
         <v>1</v>
       </c>
-      <c r="O83" t="n">
+      <c r="P83" t="n">
         <v>0</v>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -6309,12 +6560,15 @@
         </is>
       </c>
       <c r="N84" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="O84" t="n">
         <v>1</v>
       </c>
-      <c r="O84" t="n">
+      <c r="P84" t="n">
         <v>0</v>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -6379,12 +6633,15 @@
         </is>
       </c>
       <c r="N85" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="O85" t="n">
         <v>1</v>
       </c>
-      <c r="O85" t="n">
+      <c r="P85" t="n">
         <v>0</v>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -6449,12 +6706,15 @@
         </is>
       </c>
       <c r="N86" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="O86" t="n">
         <v>1</v>
       </c>
-      <c r="O86" t="n">
+      <c r="P86" t="n">
         <v>0</v>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -6519,12 +6779,15 @@
         </is>
       </c>
       <c r="N87" t="n">
+        <v>-0.2001</v>
+      </c>
+      <c r="O87" t="n">
         <v>0.4</v>
       </c>
-      <c r="O87" t="n">
+      <c r="P87" t="n">
         <v>0.6</v>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>negative</t>
         </is>
@@ -6589,12 +6852,15 @@
         </is>
       </c>
       <c r="N88" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="O88" t="n">
         <v>1</v>
       </c>
-      <c r="O88" t="n">
+      <c r="P88" t="n">
         <v>0</v>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -6659,12 +6925,15 @@
         </is>
       </c>
       <c r="N89" t="n">
+        <v>0.1975</v>
+      </c>
+      <c r="O89" t="n">
         <v>0.6</v>
       </c>
-      <c r="O89" t="n">
+      <c r="P89" t="n">
         <v>0.4</v>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -6729,12 +6998,15 @@
         </is>
       </c>
       <c r="N90" t="n">
+        <v>0.5992</v>
+      </c>
+      <c r="O90" t="n">
         <v>0.8</v>
       </c>
-      <c r="O90" t="n">
+      <c r="P90" t="n">
         <v>0.2</v>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -6799,12 +7071,15 @@
         </is>
       </c>
       <c r="N91" t="n">
+        <v>0.5992</v>
+      </c>
+      <c r="O91" t="n">
         <v>0.8</v>
       </c>
-      <c r="O91" t="n">
+      <c r="P91" t="n">
         <v>0.2</v>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -6869,12 +7144,15 @@
         </is>
       </c>
       <c r="N92" t="n">
+        <v>0.9898</v>
+      </c>
+      <c r="O92" t="n">
         <v>1</v>
       </c>
-      <c r="O92" t="n">
+      <c r="P92" t="n">
         <v>0</v>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
@@ -6939,12 +7217,15 @@
         </is>
       </c>
       <c r="N93" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="O93" t="n">
         <v>1</v>
       </c>
-      <c r="O93" t="n">
+      <c r="P93" t="n">
         <v>0</v>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
